--- a/2022 data/excel_outputs/290_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/290_boothwise_data.xlsx
@@ -14,675 +14,1509 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="523">
   <si>
     <t>AC 290 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>#nn####nn##nn ;1.8ddh ############# ###### ###</t>
-  </si>
-  <si>
-    <t>#nn ####nn ##nn ;1.8ddh ############# ####### ###</t>
-  </si>
-  <si>
-    <t>#nn ####nn ##nn ;1.8ddh ########## ###### ###</t>
-  </si>
-  <si>
-    <t>#nn ####nn ##nn ;1.8ddh ########## ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn ####nn ##nn ;1.8ddh ########## ####### ###</t>
-  </si>
-  <si>
-    <t>#nn ####nn ##nn ;1.8ddh ######## #### #nn 1</t>
-  </si>
-  <si>
-    <t>#nn ####nn ##nn ;1.8ddh ######## #### #nn 2</t>
-  </si>
-  <si>
-    <t>#nn ####nn ##nn ;1.8ddh ######## ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ####### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ####### ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######## #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######## ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn #####</t>
-  </si>
-  <si>
-    <t>##nn##nn##nn ##########</t>
-  </si>
-  <si>
-    <t>####nn##nn #########</t>
-  </si>
-  <si>
-    <t>####nn##nn ########## #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ########## ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ########### #### ##nn1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ########### ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn #######</t>
-  </si>
-  <si>
-    <t>####nn##nn ########### ###### ###</t>
-  </si>
-  <si>
-    <t>####nn##nn ########### ####### ###</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ##### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ##### ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ####### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ####### ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh #### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh #### ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############ #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############ #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############ ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ######### ####### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ######### ####### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####nn##nn ######### ####### ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ############## #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ############## ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ##########</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ########### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ########### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############## #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############## #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############## #### ##nn 3</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############## #### ##nn 4</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############## ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ########</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ###### ###### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ###### ###### ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh #######</t>
-  </si>
-  <si>
-    <t>####nn##nn ######### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ######### ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ###### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ###### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>###### ### ##### ############# #### ##nn 1</t>
-  </si>
-  <si>
-    <t>###### ### ##### ############# #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#### #nn##nn##nn ######## #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#### #nn##nn##nn ######## #### ##nn 3</t>
-  </si>
-  <si>
-    <t>#### #nn##nn##nn ######## #### ##nn 4</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ########### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ##### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ##### ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############# #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############# #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######### #### ##nn 3</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ###### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ###### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####nn##nn ##########</t>
-  </si>
-  <si>
-    <t>####nn##nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############ #### ##nn 3</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############ #### ##nn 4</t>
-  </si>
-  <si>
-    <t>####nn##nn ########### #############</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ##### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ##### ###nn #### 2</t>
-  </si>
-  <si>
-    <t>####nn##nn ########### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ########### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####nn##nn ########### ###nn #### 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ########### ###nn #### 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############</t>
-  </si>
-  <si>
-    <t>####nn##nn ###### ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ######## #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ######## #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####nn##nn ######## ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ######## #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nnnn ######## #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn ####nn##nn;1.8ddh ###### ##### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn;1.8ddh ########### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############### ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############### #### ##nn 3</t>
-  </si>
-  <si>
-    <t>####nn##nn ########## #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh #########</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ###### ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ##############</t>
-  </si>
-  <si>
-    <t>#nn ####nn ##nn ;1.8ddh ####### #### #nn 1</t>
-  </si>
-  <si>
-    <t>#nn ####nn ##nn ;1.8ddh ####### #### #nn 2</t>
-  </si>
-  <si>
-    <t>#nn ####nn ##nn ;1.8ddh ####### ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh #####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ####### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>##nn##nn##nn ########</t>
-  </si>
-  <si>
-    <t>##### #### ##### ########## #### ##nn 1</t>
-  </si>
-  <si>
-    <t>##### #### ##### ########## #### ##nn 2</t>
-  </si>
-  <si>
-    <t>##### #### ##### ########## #### ##nn 3</t>
-  </si>
-  <si>
-    <t>##### #### ##### ########## #### ##nn 4</t>
-  </si>
-  <si>
-    <t>####nn##nn ################# #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ################# ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ###########</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ###########</t>
-  </si>
-  <si>
-    <t>####nn##nn ############# ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ############# #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn #############</t>
-  </si>
-  <si>
-    <t>####nn##nn ############## #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######</t>
-  </si>
-  <si>
-    <t>####nn##nn ########</t>
-  </si>
-  <si>
-    <t>####nn##nn ###### ###### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ###### ###### ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ######### ###### ###</t>
-  </si>
-  <si>
-    <t>####nn##nn ######### ####### ###</t>
-  </si>
-  <si>
-    <t>####nn##nn ###### ###### ###</t>
-  </si>
-  <si>
-    <t>####nn##nn ########### ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ########### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####nn##nn ######</t>
-  </si>
-  <si>
-    <t>####nn##nn ############</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############# ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ##### ####### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ##### ####### ###nn ####</t>
-  </si>
-  <si>
-    <t>#### #### #### ##nn ####nn ##### ##### ###### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#### #### #### ##nn ####nn ##### ##### ###### #### ##nn 5</t>
-  </si>
-  <si>
-    <t>#### #### #### ##nn ####nn ##### ##### ###### #### ##nn 4</t>
-  </si>
-  <si>
-    <t>#### #### #### ##nn ####nn ##### ##### ###### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#### #### #### ##nn ####nn ##### ##### ###### #### ##nn 3</t>
-  </si>
-  <si>
-    <t>#### #### #### ##nn ####nn ##### ##### ###### #### ##nn 6</t>
-  </si>
-  <si>
-    <t>####nn##nn #### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn #### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######## #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####nn##nn ####### ######</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh #### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ############ #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ############ #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ###### ########</t>
-  </si>
-  <si>
-    <t>####nn##nn ######## #######</t>
-  </si>
-  <si>
-    <t>##nn##nn##nn ###### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>##nn##nn##nn ###### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ########## #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ########## #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####nn##nn ############# #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ###### ###########</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh #############</t>
-  </si>
-  <si>
-    <t>####nn##nn ########## ##### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ########## ##### ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######### ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh #################nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ##### ###</t>
-  </si>
-  <si>
-    <t>####nn##nn ############ ###### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ############ ###### ###nn ####</t>
-  </si>
-  <si>
-    <t>##### ####nn##nn ###### ####### ###</t>
-  </si>
-  <si>
-    <t>##### ####nn##nn ###### ###nn ####</t>
-  </si>
-  <si>
-    <t>##### ####nn##nn ###### #### ###</t>
-  </si>
-  <si>
-    <t>##### ####nn##nn ###### ###nn #### 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ####### #####</t>
-  </si>
-  <si>
-    <t>####nn##nn ####### #####</t>
-  </si>
-  <si>
-    <t>####nn##nn ########## #### ##nn 3</t>
-  </si>
-  <si>
-    <t>####nn##nn ##### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####nn##nn ######## ####### ###### ###</t>
-  </si>
-  <si>
-    <t>####nn##nn ######## ####### ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ############ #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ############ #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ########## ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ######### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ######### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ######### ###nn ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ##### ######nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ##### ######nn 2</t>
-  </si>
-  <si>
-    <t>####nn##nn ###### ########</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ##### ##### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ##### ##### ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ##### ##### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ##### ##### #### ##nn 3</t>
-  </si>
-  <si>
-    <t>### ### #### ##### ##### #### ##nn 1 ;## ########ddh</t>
-  </si>
-  <si>
-    <t>### ### #### ##### ##### #### ##nn 2 ;## ########ddh</t>
-  </si>
-  <si>
-    <t>### ### #### ##### ##### #### ##nn 3 ;## ########ddh</t>
-  </si>
-  <si>
-    <t>### ### #### ##### ##### #### ##nn 4 ;## ########ddh</t>
-  </si>
-  <si>
-    <t>### ### #### ##### ##### #### ##nn 5 ;## ########ddh</t>
-  </si>
-  <si>
-    <t>######### ####nn##nn ##### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>######### ####nn##nn ##### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>######### ####nn##nn ##### #### ##nn 3</t>
-  </si>
-  <si>
-    <t>######### ####nn##nn ##### #### 4</t>
-  </si>
-  <si>
-    <t>### ### #### ##### ##### #### ##nn 1 ;###### ########ddh</t>
-  </si>
-  <si>
-    <t>### ### #### ##### ##### #### ##nn 6 ;###### ########ddh</t>
-  </si>
-  <si>
-    <t>### ### #### ##### ##### #### ##nn 2 ;###### ########ddh</t>
-  </si>
-  <si>
-    <t>### ### #### ##### ##### #### ##nn 3 ;###### ########ddh</t>
-  </si>
-  <si>
-    <t>### ### #### ##### ##### #### ##nn 4 ;###### ########ddh</t>
-  </si>
-  <si>
-    <t>### ### #### ##### ##### #### ##nn 5 ;###### ########ddh</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ####### ############</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ################## #### ##nn 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ################## ###nn ####</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######### ###### ###</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######### ####### ###</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######### ### ####</t>
-  </si>
-  <si>
-    <t>####nn##nn ############ ###nn ####</t>
-  </si>
-  <si>
-    <t>##nn##nn##nn ######## #####</t>
-  </si>
-  <si>
-    <t>####nn##nn ############### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn ############### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############ ###### ###</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ############ ####### ###</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######## ###### ###</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ######## ####### ###</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ########### ###### ###</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ########### ###nn #### 1</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ########### ###nn #### 2</t>
-  </si>
-  <si>
-    <t>#nn####nn##nn ;1.8ddh ########### ####### ###</t>
-  </si>
-  <si>
-    <t>####nn##nn ####### ### ####</t>
-  </si>
-  <si>
-    <t>####nn##nn #### #### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####nn##nn #### #### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>###### ###### ## ####### ######## ######</t>
-  </si>
-  <si>
-    <t>####nn##nn ####### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>###### ### ####### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>###### ### ####### #### ##nn 2</t>
+    <t>A0 V0 RAJAPUR PURAINA (PUV BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 RAJAPUR PURAINA (PASH CHAMI BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 TAVAR GAMV (PUV BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 TAVAR GAMV (PASH CHAMI BHAG)</t>
+  </si>
+  <si>
+    <t>U0 A0 V0 KUI BHAYA K SAM01</t>
+  </si>
+  <si>
+    <t>U0 A0 V0 KUI BHAYA A T0K</t>
+  </si>
+  <si>
+    <t>A0 V0 BEGAMAPUR</t>
+  </si>
+  <si>
+    <t>A0 V0 HARABAMSHAPUR</t>
+  </si>
+  <si>
+    <t>A0 V0 J%D</t>
+  </si>
+  <si>
+    <t>A0 V0 '(LOKAPUR</t>
+  </si>
+  <si>
+    <t>A0 V0 RAHAMATAG U AMV</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAUR KO,TAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 BANAKATAVA MAHOL</t>
+  </si>
+  <si>
+    <t>A0 V0 RANIPUR</t>
+  </si>
+  <si>
+    <t>A0 V0 MANAV.RAYA BOJHA (U0 BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 MANAV.RAYA BOJHA (D0 BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 DOD PURAVA</t>
+  </si>
+  <si>
+    <t>A0 V0 DE VARA</t>
+  </si>
+  <si>
+    <t>A0 V0 ALAGAMV</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAMARAPURAVA</t>
+  </si>
+  <si>
+    <t>A0 V0 NADAIDIH (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 NADAIDIH (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 BADHANI</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 MANAV.RAYA D VAN (K0SAM01)</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 MANAV.RAYA D VAN (K0SAM02)</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 MANAV.RAYA D VAN (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 IM5LAYA KARANAPUR (U0 BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 IM5LAYA KARANAPUR (D0 BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 5MAJA6PUR DA0 PATAPARAGAMJ (U0 BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 5MAJA6PUR DA0 PATAPARAGAMJ (D0 BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 MAHADE V SALARAPUR (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 MAHADE V SALARAPUR (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 DAM.DEKUMIYA</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL GAYAD9TAPURAVA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL GAYAD9TAPARU VA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL GAYAD9TAPARU VA (K0SAM03)</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL GAYAD9TAPARU VA (A T0K )</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL HARAD9TANAGAR GAR:T (K0SAM01)</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL HARAD9TANAGAR GAR:T (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 HARAD9TANAGAR GAR:T (U0BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 HARAD9TANAGAR GAR:T (D0BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 BABHANAPARU VA</t>
+  </si>
+  <si>
+    <t>U0 A0 V0 LALAPARU (K0SAM01)</t>
+  </si>
+  <si>
+    <t>U0 A0 V0 LALAPARU (A T0 K )</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAUBEDIH</t>
+  </si>
+  <si>
+    <t>A0 V0 BAIJANATHAPARU (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 BAIJANATHAPARU (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 BAHORAVA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 BAHORAVA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0UDALAHAVA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0UDALAHAVA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL CHARAIYA RANISIR (K0SAM01)</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL CHARAIYA RANISIR (K0SAM02)</t>
+  </si>
+  <si>
+    <t>JANATA J0U HA08KUL MAHADE VA NA5SARAGAMJ (K0SAM01)</t>
+  </si>
+  <si>
+    <t>JANATA J0U HA08KUL MAHADE VA NA5SARAGAMJ (K0SAM03)</t>
+  </si>
+  <si>
+    <t>JANATA J0U HA08KUL MAHADE VA NA5SARAGAMJ (K0SAM04)</t>
+  </si>
+  <si>
+    <t>A0 V0 CH&lt;DAN KO,TAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAJARU (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAJARU (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAGAVANAPARU DAG U A6PARU (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAGAVANAPARU DAG U A6PARU (A T0K )</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL DAMAP U RU VA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL DAMAP U RU VA (K0SAM03)</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL DAMAP U RU VA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAL PHATAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 SATARAH</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAUGOI (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAUGOI (A T0K )</t>
+  </si>
+  <si>
+    <t>PU0 MA0 V0 GAUSAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 GOPALASARAY</t>
+  </si>
+  <si>
+    <t>A0 V0 ASANI</t>
+  </si>
+  <si>
+    <t>A0 V0 SHAHAPARU BHATAPARU VA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 SHAHAPARU BHATAPARU VA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>DY0 J0 KDYATHABHLABH K|CH SHR6THABHDY YACH0JBH|THABHDYAS|KKBH</t>
+  </si>
+  <si>
+    <t>KL0 SHR0 J~NAKL|JBH|THABHS|THABH J~NADYABBH AIBHT6JBH|THABHKL L|SHRCH0SHRATHABHDYAJBH|THABHKL|AIDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>AIBHT0CH THABHDY08SHRCH|CHAI KDYATHABHLABH K|CH SHR6THABHDY</t>
+  </si>
+  <si>
+    <t>A0 V0 U MEDAPARU VA DA0 T@DAA U BARAV</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 DADAURA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 DADAURA (A T0K )</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 DADAURA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 PHULAV.RAYA SHAHAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 5SATAKAHANA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 5SATAKAHANA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU B8TI (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU B8TI (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU B8TI (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 NEVADA JAMADAR</t>
+  </si>
+  <si>
+    <t>A0 V0 BARAGADAH (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 BARAGADAH (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 DE VAR NAYA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 DE VAR NAYA (A T0K )</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN DE VAR NAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 DHAS U VA</t>
+  </si>
+  <si>
+    <t>A0 V0 5BH,THAYA CHACH.DI</t>
+  </si>
+  <si>
+    <t>A0 V0 CH&lt;BKHA BAJ U G 6U (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 CH&lt;BKHA BAJ U G 6U (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 CH&lt;BKHA BAJ U G 6U (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 PAPAR</t>
+  </si>
+  <si>
+    <t>A0 V0 ADARAI</t>
+  </si>
+  <si>
+    <t>A0 V0 TAL U SIPARU (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 TAL U SIPARU (PICCHAMI BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 M NAHARATARA</t>
+  </si>
+  <si>
+    <t>A0 V0 U9TAMAPARU</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL ,DAKAUL (K0SAM01)</t>
+  </si>
+  <si>
+    <t>J0U HA08KUL ,DAKAUL (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 LOHARASAPARU NARAHA</t>
+  </si>
+  <si>
+    <t>A0 V0 GAJ U RAVARA</t>
+  </si>
+  <si>
+    <t>A0 V0 MALABHAUKHARA</t>
+  </si>
+  <si>
+    <t>A0 V0 MOHAR NAYA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 MOHAR NAYA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 KAK&lt;DHU (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 KAK&lt;DHU (A T0K )</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 BARADE HARA BHAR GAMV (K0SAM01)</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 BARADE HARA BHAR GAMV (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 LAL KAI&lt;DAA U</t>
+  </si>
+  <si>
+    <t>A0 V0 AKARA</t>
+  </si>
+  <si>
+    <t>A0 V0 NEV.RAYA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 NEV.RAYA(A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 NEV.RAYA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 RAGHUNATHAPARU</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 LAKHAH KAS</t>
+  </si>
+  <si>
+    <t>FK0I0KALEJ LAGMANANAGAR (K0SAM01)</t>
+  </si>
+  <si>
+    <t>FK0I0KALEJ LAGMANANAGAR (K0SAM03)</t>
+  </si>
+  <si>
+    <t>FK0I0KALEJ LAGMANANAGAR (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 NIBABHAR</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAVANI NAGAR</t>
+  </si>
+  <si>
+    <t>A0 V0 FKASHUNAPARU CH&lt;DANABHAR (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 FKASHUNAPARU CH&lt;DANABHAR (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 BAIRAGIPARU VA DA0 KHARAK,HAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 NAKAHA DHAM6NAGAR</t>
+  </si>
+  <si>
+    <t>A0 V0 NARAYANAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 K5SAYAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 PAKAHDAYA DA. RAMANAGARA</t>
+  </si>
+  <si>
+    <t>A0 V0 KAIYANAPARU (PAV U BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 KAIYANAPARU (PICCHAMI BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 VASHUNAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 HALADA</t>
+  </si>
+  <si>
+    <t>A0 V0 I5M5LAYA NARAYAN(K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 I5M5LAYA NARAYAN (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 SHAHAPARU KATHAU TAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 DAB U KALA (U0BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 DAB U KALA (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAIRAKALA</t>
+  </si>
+  <si>
+    <t>A0 V0 A,HARAGHASI</t>
+  </si>
+  <si>
+    <t>A0 V0 GHORAMA PAR5SAYA (U0BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 GHORAMA PAR5SAYA (D0BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 PACHADE VAR MAPHAJ</t>
+  </si>
+  <si>
+    <t>A0 V0 L@GADI GAL U R</t>
+  </si>
+  <si>
+    <t>A0 V0 M NAKAPARU KHAD U 6</t>
+  </si>
+  <si>
+    <t>A0 V0 GAT U U HAK (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 GAT U U HAK (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 DHAISARA</t>
+  </si>
+  <si>
+    <t>A0 V0 H.RAHARAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 TARU HANI BALARAM</t>
+  </si>
+  <si>
+    <t>A0 V0 RATANAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 BARAVAM HARAGAN U</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU KO.DAR</t>
+  </si>
+  <si>
+    <t>A0 V0 AURAIYA ,TAKAI</t>
+  </si>
+  <si>
+    <t>A0 V0 EKADAGAVA</t>
+  </si>
+  <si>
+    <t>A0 V0 BHARAU.DA</t>
+  </si>
+  <si>
+    <t>A0 V0 MIRAMAU</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAUSAVAM (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAUSAVAM (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 CH&lt;DANA BADHAITARA</t>
+  </si>
+  <si>
+    <t>A0 V0KESHAVAPARU PAJAVA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0KESHAVAPARU PAJAVA (A T0K )</t>
+  </si>
+  <si>
+    <t>DY0 J0 THABHCH|PDYACHBBHDYABBHDYAJCH SHRCH|THABHLABH CH THABHDYAJ</t>
+  </si>
+  <si>
+    <t>A0 V0 SONAVA</t>
+  </si>
+  <si>
+    <t>A0 V0 GALAUL</t>
+  </si>
+  <si>
+    <t>A0 V0 BELAVA KHATIB</t>
+  </si>
+  <si>
+    <t>A0 V0 KURABENI</t>
+  </si>
+  <si>
+    <t>A0 V0 VAJAYAPARU 5SASAVAM</t>
+  </si>
+  <si>
+    <t>A0 V0 PARE VAPARU (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 PARE VAPARU (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 MAHOR DA.BAGAVANI(K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 MAHOR DA. BAGAVANI (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 MANOHARAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 AGARADIHA</t>
+  </si>
+  <si>
+    <t>A0 V0 VAMTAVARA</t>
+  </si>
+  <si>
+    <t>A0 V0 5BHAKHAR PARU MASADH</t>
+  </si>
+  <si>
+    <t>A0 V0 D&lt;DAUL</t>
+  </si>
+  <si>
+    <t>GAUR SHAMKAR T:DAN NE08MA0I0KA0 GALAULA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>GAUR SHAMKAR T:DAN NE08MA0I0KA0 GALAULA (K0SAM04)</t>
+  </si>
+  <si>
+    <t>GAUR SHAMKAR T:DAN NE08MA0I0KA0 GALAULA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>GAUR SHAMKAR T:DAN NE08MA0I0KA0 GALAULA (K0SAM03)</t>
+  </si>
+  <si>
+    <t>A0 V0 CH&lt;BAVAM</t>
+  </si>
+  <si>
+    <t>A0 V0 TALAKAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 AURAIYA NADHAN</t>
+  </si>
+  <si>
+    <t>A0 V0 5BHATHAURA RAM SAHAY</t>
+  </si>
+  <si>
+    <t>A0 V0 KATAHA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 KATAHA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 DAMAMA</t>
+  </si>
+  <si>
+    <t>A0 V0 GOPALAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 NAGARAURA</t>
+  </si>
+  <si>
+    <t>A0 V0 CHE TAYA MARU AR (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 CHE TAYA MARU AR (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 KASHIPARU MAS U A</t>
+  </si>
+  <si>
+    <t>A0 V0 5SAMHANAJOT ,DAKAUL</t>
+  </si>
+  <si>
+    <t>A0 V0 LAKHANA</t>
+  </si>
+  <si>
+    <t>A0 V0 HDAKARA</t>
+  </si>
+  <si>
+    <t>A0 V0 KATAR (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 KATAR (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 RAYAPARU 'BALELA(K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 RAYAPARU 'BALELA(A T.K )</t>
+  </si>
+  <si>
+    <t>A0 V0 KAIYANAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 RAYAPARU PAYARE</t>
+  </si>
+  <si>
+    <t>A0 V0HARAVAMSHAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 K@VATANAPARU VA DA0BAGANAHA</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMANAGAR DA0 KERAV NAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAGढ़</t>
+  </si>
+  <si>
+    <t>A0 V0 SEH NAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 GAUH NAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 H.RAHARAPARU DA0 MAQY NAGAR</t>
+  </si>
+  <si>
+    <t>|0 T0 CHGH N AIBHV9J|D|CH|TN</t>
+  </si>
+  <si>
+    <t>A0 V0 BHARATHAPARU (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 BHARATHAPARU (A T.K )</t>
+  </si>
+  <si>
+    <t>A0 V0 PATAKHAUL KALA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0PATAKHAUL KALA (A T.K )</t>
+  </si>
+  <si>
+    <t>A0 V0 M NAKAURA</t>
+  </si>
+  <si>
+    <t>A0 V0 SHAHAPARU BARA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 S'U BAKHA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 S'U BAKHA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 MANASAKH U A</t>
+  </si>
+  <si>
+    <t>A0 V0 PAPARA</t>
+  </si>
+  <si>
+    <t>A0 V0 EKAGHARAVA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 EKAGHARAVA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU PAI.DA (NAYA BHAVAN K SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU PAI.DA (NAYA BHAVAN K SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 GO.DAR</t>
+  </si>
+  <si>
+    <t>A0 V0 KHADAILA DA0 KAMALABHAR (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 KHADAILA DA0 KAMALABHAR (K0SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 MOH DAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 R@ DAGAVAM DA0 RANIPARU QAZI</t>
+  </si>
+  <si>
+    <t>A0 V0 KOTAMAB U ARAKAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 RAJAPARU KHAD U 6</t>
+  </si>
+  <si>
+    <t>A0 V0 JAYACH&lt;DAPARU KATAGHARA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 JAYACH&lt;DAPARU KATAGHARA (K0SAM02)</t>
+  </si>
+  <si>
+    <t>DY0 J0 |PDYACHALABHBBHDYAJCH YASHRCH0|PDYAK01KKBH</t>
+  </si>
+  <si>
+    <t>DY0 J0 |PDYACHALABHBBHDYAJCH YASHRCH0|PDYAK02KKBH</t>
+  </si>
+  <si>
+    <t>A0 V0 SARAVAN TARA</t>
+  </si>
+  <si>
+    <t>A0 V0 MAHADE V JAGAD SH</t>
+  </si>
+  <si>
+    <t>A0 V0 BASABH.RAYA PARU AINA (K0SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 BASABH.RAYA PARU AINA (A T. K )</t>
+  </si>
+  <si>
+    <t>A0 V0 LAUKHIBHAR</t>
+  </si>
+  <si>
+    <t>A0 V0 AVTAR NAGAR</t>
+  </si>
+  <si>
+    <t>A0 V0 JANAKAJ NAGAR KHAD U 6</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAUKAJDARAPARU VA SEMAGADHA (K SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAUKAJDARAPARU VA SEMAGADHA (A T0 K )</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 SEMAGADHA (PICCHAMI BHAG)</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 SEMAGADHA (A T0 K )</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 SEMAGADHA (MAQY BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 KOLABHAR MAJAGAVA (K SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 KOLABHAR MAJAGAVA (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU KATE L</t>
+  </si>
+  <si>
+    <t>NAV A0 V0 LALAPARU KHADARA (K SAM01)</t>
+  </si>
+  <si>
+    <t>NAV A0 V0 LALAPARU KHADARA (K SAM02)</t>
+  </si>
+  <si>
+    <t>NAV A0 V0 LALAPARU KHADARA (K SAM03)</t>
+  </si>
+  <si>
+    <t>A0 V0 KU HARAGADH</t>
+  </si>
+  <si>
+    <t>A0 V0 RANIKU:DA</t>
+  </si>
+  <si>
+    <t>A0 V0 BARAIPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 ITAWJHA</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAMEPARA DA0 IMTAV.RAYA (U0BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAMEPARA DA0 IMTAV.RAYA (A T0K )</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAMEPARA DA0 IMTAV.RAYA (MAQYABHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 CHACH.DI (K SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 CHACH.DI (K SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 KAILASHAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAGAVANAPARU BANAKAT (K SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAGAVANAPARU BANAKAT (K SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU BANAKAT T:DAVA MAH&lt;TH(K SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU BANAKAT T:DAVA MAH&lt;TH(A T0K )</t>
+  </si>
+  <si>
+    <t>U0◌ A0 V0 SITAZVAR (K SAM01)</t>
+  </si>
+  <si>
+    <t>U0◌ A0 V0 SITAZVAR (K SAM02)</t>
+  </si>
+  <si>
+    <t>|0 T0 TH|KBH|PKHL|</t>
+  </si>
+  <si>
+    <t>A0 V0 PARASAURA MAFAJ</t>
+  </si>
+  <si>
+    <t>A0 V0 SONARAI</t>
+  </si>
+  <si>
+    <t>A0 V0 MADARA</t>
+  </si>
+  <si>
+    <t>A0 V0 JAMUNAHA DA0 MOHANIPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 MI8J,DAYA BHAL,U HAYA DASAWDHI</t>
+  </si>
+  <si>
+    <t>A0 V0 N9THAPARU VA (K SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 N9THAPARU VA (K SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 N9THAPARU VA (A T. K )</t>
+  </si>
+  <si>
+    <t>K0PU0 A0 V0 IKAUNA (K SAM.1)</t>
+  </si>
+  <si>
+    <t>K0PU0 A0 V0 IKAUNA (A T. K )</t>
+  </si>
+  <si>
+    <t>K0PU0 A0 V0 IKAUNA (K SAM.2)</t>
+  </si>
+  <si>
+    <t>K0PU0 A0 V0 IKAUNA (K SAM.3)</t>
+  </si>
+  <si>
+    <t>KE&lt;B Y A0 V0 IKAUNA (K SAM01)</t>
+  </si>
+  <si>
+    <t>KE&lt;B Y A0 V0 IKAUNA (K SAM02)</t>
+  </si>
+  <si>
+    <t>KE&lt;B Y A0 V0 IKAUNA (K SAM03)</t>
+  </si>
+  <si>
+    <t>KE&lt;B Y A0 V0 IKAUNA (A T0K )</t>
+  </si>
+  <si>
+    <t>JAGATAJIT I0KA0 IKAUNA (PURANI 'BIIDAMG K SAM01)</t>
+  </si>
+  <si>
+    <t>JAGATAJIT I0KA0 IKAUNA (PURANI 'BIIDAMG K SAM02)</t>
+  </si>
+  <si>
+    <t>JAGATAJIT I0KA0 IKAUNA(PARU ANI 'BIIDAMGAK SAM03)</t>
+  </si>
+  <si>
+    <t>JAGATAJIT I0KA0 IKAUNA(PARU ANI 'BIIDAMGAK SAM04)</t>
+  </si>
+  <si>
+    <t>JAGATAJIT I0KA0 IKAUNA(PARU ANI 'BIIDAMGAK SAM05)</t>
+  </si>
+  <si>
+    <t>VAKAS KH:D KAYA6LAY IKAUNA HॉL KAMARA</t>
+  </si>
+  <si>
+    <t>VAKAS KH:D KAYA6LAY IKAUNA SABHA K</t>
+  </si>
+  <si>
+    <t>A0 V0 MAJHAUVA SUMAL (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 MAJHAUVA SUMAL (K SAM.2)</t>
+  </si>
+  <si>
+    <t>A0 V0 MOH MADAPARU RAJA (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 MOH MADAPARU RAJA (A T.K )</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPARU VA DA. M NAKAURA KO.DAR</t>
+  </si>
+  <si>
+    <t>A0 V0 AMDHARAPARU VA (NAYA BHAVAN)</t>
+  </si>
+  <si>
+    <t>A0 V0 I5M5LAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 MAHARAUL</t>
+  </si>
+  <si>
+    <t>A0 V0 KOTAVA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 DAHAVAR KALA</t>
+  </si>
+  <si>
+    <t>A0 V0 5SHAVAJOT</t>
+  </si>
+  <si>
+    <t>A0 V0 BHOJAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 A,HARANAPARU VA DA. BELAKAR</t>
+  </si>
+  <si>
+    <t>A0 V0 MAJ U H NAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 DHAM6PARU</t>
+  </si>
+  <si>
+    <t>A0 V0 LAGMANAPARU GODAPARU VA</t>
+  </si>
+  <si>
+    <t>A0 V0 GANESHAPARU</t>
+  </si>
+  <si>
+    <t>J.U HA. 8KUL SEMAR TARAHAR (K SAM.1)</t>
+  </si>
+  <si>
+    <t>J.U HA. 8KUL SEMAR TARAHAR (K SAM.2)</t>
+  </si>
+  <si>
+    <t>A0 V0 GANESHIJOT</t>
+  </si>
+  <si>
+    <t>A0 V0 MANOHARAPARU (PAV U BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 MANOHARAPARU (PICCHAMI BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 MANOHARAPARU (HॉL KAMARA)</t>
+  </si>
+  <si>
+    <t>A0 V0 NARAYANAJOT (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 NARAYANAJOT (K SAM.2)</t>
+  </si>
+  <si>
+    <t>A0 V0 FK,DHAYAUNA (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 FK,DHAYAUNA (A T.K )</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAT U HA</t>
+  </si>
+  <si>
+    <t>A0 V0 MALAUNA KH5SAYAR</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 PH9TAP U RU TANAJA</t>
+  </si>
+  <si>
+    <t>A0 V0 HD MGARU AJOT</t>
+  </si>
+  <si>
+    <t>A0 V0 RAJAGढ़ GAL U .RAHA (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 RAJAGढ़ GAL U .RAHA (K SAM.2)</t>
+  </si>
+  <si>
+    <t>A0 V0 MUCKABAD</t>
+  </si>
+  <si>
+    <t>A0 V0 KHARAGAURA B8TI</t>
+  </si>
+  <si>
+    <t>A0 V0 RAGHAV U IRAPARU VA DA. KHAVAMPOKHAR</t>
+  </si>
+  <si>
+    <t>A0 V0 AKABARAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 KHACH6 VIRAN</t>
+  </si>
+  <si>
+    <t>A0 V0 MAQYANAGAR MANOHARAPARU (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 MAQYANAGAR MANOHARAPARU (A T.K )</t>
+  </si>
+  <si>
+    <t>A0 V0 KAMJADAVA</t>
+  </si>
+  <si>
+    <t>A0 V0 PARU E D N NAMAGढ़ (PAV U BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 PARU E D N NAMAGढ़ (PICCHAMI BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 BAIDAURA MASH.RAK</t>
+  </si>
+  <si>
+    <t>A0 V0 GOPALAPARU (PAV U BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 GOPALAPARU (PICCHAMIBHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 T@DAA U PI:DAT</t>
+  </si>
+  <si>
+    <t>A0 V0 LAKHAH</t>
+  </si>
+  <si>
+    <t>A0 V0 AMARE BH.RAYA (K SAM01)</t>
+  </si>
+  <si>
+    <t>A0 V0 AMARE BH.RAYA (K SAM02)</t>
+  </si>
+  <si>
+    <t>A0 V0 BHATAPARU VA KHAD U 6</t>
+  </si>
+  <si>
+    <t>A0 V0 KATARA GAL U .RAHA (U0BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 KATARA GAL U .RAHA (A T.K )</t>
+  </si>
+  <si>
+    <t>A0 V0 KATARA GAL U .RAHA (D0BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 CH^BH:DAR</t>
+  </si>
+  <si>
+    <t>A0 V0 'BADAHU NI (PAV U BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 'BADAHU NI (PICCHAMI BHAG)</t>
+  </si>
+  <si>
+    <t>A0 V0 KHARAGAP U RU</t>
+  </si>
+  <si>
+    <t>A0 V0 KATAH BAGAH</t>
+  </si>
+  <si>
+    <t>A0 V0 MAHADE IYA</t>
+  </si>
+  <si>
+    <t>A0 V0 PATAKHAUL KHAD U 6</t>
+  </si>
+  <si>
+    <t>A0 V0 BELAHA RAGHAV (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 BELAHA RAGHAV (A T.K )</t>
+  </si>
+  <si>
+    <t>A0 V0 D5SAYAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU DAKAH</t>
+  </si>
+  <si>
+    <t>A0 V0 VASHUNAPARU (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 VASHUNAPARU (K SAM.2)</t>
+  </si>
+  <si>
+    <t>A0 V0 VIRAPARU MAMSHARAM (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 VIRAPARU MAMSHARAM (A T.K )</t>
+  </si>
+  <si>
+    <t>P.RAVAR KAIYAN UPAKE&lt;B KHAIRAH NAYA VIRAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 NARAPATAPARU</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT BHAVAN NARAPATAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 5SHAVAPARU BANAKAT (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 5SHAVAPARU BANAKAT (A T.K )</t>
+  </si>
+  <si>
+    <t>A0 V0 PARASHARU AMAPARU</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 TALAKAPARU (K SAM.1)</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 TALAKAPARU (K SAM.2)</t>
+  </si>
+  <si>
+    <t>A0 V0 5M`AU5LAYA (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 5M`AU5LAYA (K SAM.2)</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAINAPARU VIRAN (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAINAPARU VIRAN (A T.K )</t>
+  </si>
+  <si>
+    <t>A0 V0 JORADIH (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 JORADIH (K SAM.2)</t>
+  </si>
+  <si>
+    <t>A0 V0 LALABOJHI (K SAM.1)</t>
+  </si>
+  <si>
+    <t>A0 V0 LALABOJHI (A T.K )</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 426</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 427</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 428</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 429</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 430</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 431</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 432</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 433</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 434</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 435</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 436</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 437</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 438</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 439</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 440</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 441</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 442</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 443</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 444</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 445</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 446</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 447</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 448</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 449</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 450</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 451</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 452</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 453</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 454</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 455</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 456</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 457</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 458</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 459</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 460</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 461</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 462</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 463</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 464</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 465</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 466</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 467</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 468</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 469</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 470</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 471</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 472</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 473</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 474</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 475</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 476</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 477</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAVAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 478</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -755,8 +1589,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -772,7 +1614,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -780,12 +1622,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1084,82 +1944,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>223</v>
+        <v>501</v>
       </c>
       <c r="D2" t="s">
-        <v>224</v>
+        <v>502</v>
       </c>
       <c r="E2" t="s">
-        <v>225</v>
+        <v>503</v>
       </c>
       <c r="F2" t="s">
-        <v>226</v>
+        <v>504</v>
       </c>
       <c r="G2" t="s">
-        <v>227</v>
+        <v>505</v>
       </c>
       <c r="H2" t="s">
-        <v>228</v>
+        <v>506</v>
       </c>
       <c r="I2" t="s">
-        <v>229</v>
+        <v>507</v>
       </c>
       <c r="J2" t="s">
-        <v>230</v>
+        <v>508</v>
       </c>
       <c r="K2" t="s">
-        <v>231</v>
+        <v>509</v>
       </c>
       <c r="L2" t="s">
-        <v>232</v>
+        <v>510</v>
       </c>
       <c r="M2" t="s">
-        <v>233</v>
+        <v>511</v>
       </c>
       <c r="N2" t="s">
-        <v>234</v>
+        <v>512</v>
       </c>
       <c r="O2" t="s">
-        <v>235</v>
+        <v>513</v>
       </c>
       <c r="P2" t="s">
-        <v>236</v>
+        <v>514</v>
       </c>
       <c r="Q2" t="s">
-        <v>237</v>
+        <v>515</v>
       </c>
       <c r="R2" t="s">
-        <v>238</v>
+        <v>516</v>
       </c>
       <c r="S2" t="s">
-        <v>239</v>
+        <v>517</v>
       </c>
       <c r="T2" t="s">
-        <v>240</v>
+        <v>518</v>
       </c>
       <c r="U2" t="s">
-        <v>241</v>
+        <v>519</v>
       </c>
       <c r="V2" t="s">
-        <v>242</v>
+        <v>520</v>
       </c>
       <c r="W2" t="s">
-        <v>243</v>
+        <v>521</v>
       </c>
       <c r="X2" t="s">
-        <v>244</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1167,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>1149</v>
@@ -1241,7 +2170,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>1159</v>
@@ -1315,7 +2244,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>766</v>
@@ -1389,7 +2318,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>638</v>
@@ -1463,7 +2392,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>982</v>
@@ -1537,7 +2466,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>1133</v>
@@ -1611,7 +2540,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>836</v>
@@ -1685,7 +2614,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>578</v>
@@ -1759,7 +2688,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>879</v>
@@ -1833,7 +2762,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>811</v>
@@ -1907,7 +2836,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>683</v>
@@ -1981,7 +2910,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>680</v>
@@ -2055,7 +2984,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>463</v>
@@ -2129,7 +3058,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>1059</v>
@@ -2203,7 +3132,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>838</v>
@@ -2277,7 +3206,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C18">
         <v>776</v>
@@ -2351,7 +3280,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <v>795</v>
@@ -2425,7 +3354,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C20">
         <v>711</v>
@@ -2499,7 +3428,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C21">
         <v>661</v>
@@ -2573,7 +3502,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <v>1089</v>
@@ -2647,7 +3576,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>1049</v>
@@ -2721,7 +3650,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>870</v>
@@ -2795,7 +3724,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>631</v>
@@ -2869,7 +3798,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C26">
         <v>720</v>
@@ -2943,7 +3872,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>629</v>
@@ -3017,7 +3946,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>897</v>
@@ -3091,7 +4020,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>779</v>
@@ -3165,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>871</v>
@@ -3239,7 +4168,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>755</v>
@@ -3313,7 +4242,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="C32">
         <v>887</v>
@@ -3387,7 +4316,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <v>909</v>
@@ -3461,7 +4390,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <v>806</v>
@@ -3535,7 +4464,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>773</v>
@@ -3609,7 +4538,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>1043</v>
@@ -3683,7 +4612,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>990</v>
@@ -3757,7 +4686,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>803</v>
@@ -3831,7 +4760,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>1198</v>
@@ -3905,7 +4834,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>1108</v>
@@ -3979,7 +4908,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C41">
         <v>812</v>
@@ -4053,7 +4982,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>1076</v>
@@ -4127,7 +5056,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>1134</v>
@@ -4201,7 +5130,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>812</v>
@@ -4275,7 +5204,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>886</v>
@@ -4349,7 +5278,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>878</v>
@@ -4423,7 +5352,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>1077</v>
@@ -4497,7 +5426,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>907</v>
@@ -4571,7 +5500,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>904</v>
@@ -4645,7 +5574,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="C50">
         <v>988</v>
@@ -4719,7 +5648,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>1113</v>
@@ -4793,7 +5722,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C52">
         <v>861</v>
@@ -4867,7 +5796,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>852</v>
@@ -4941,7 +5870,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>1189</v>
@@ -5015,7 +5944,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>706</v>
@@ -5089,7 +6018,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>565</v>
@@ -5163,7 +6092,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C57">
         <v>814</v>
@@ -5237,7 +6166,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="C58">
         <v>1117</v>
@@ -5311,7 +6240,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C59">
         <v>875</v>
@@ -5385,7 +6314,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="C60">
         <v>310</v>
@@ -5459,7 +6388,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>1245</v>
@@ -5533,7 +6462,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="C62">
         <v>768</v>
@@ -5607,7 +6536,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>1215</v>
@@ -5681,7 +6610,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C64">
         <v>965</v>
@@ -5755,7 +6684,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="C65">
         <v>1170</v>
@@ -5829,7 +6758,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="C66">
         <v>869</v>
@@ -5903,7 +6832,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>1180</v>
@@ -5977,7 +6906,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>1088</v>
@@ -6051,7 +6980,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="C69">
         <v>1148</v>
@@ -6125,7 +7054,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C70">
         <v>939</v>
@@ -6199,7 +7128,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>861</v>
@@ -6273,7 +7202,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>852</v>
@@ -6347,7 +7276,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>667</v>
@@ -6421,7 +7350,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>984</v>
@@ -6495,7 +7424,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="C75">
         <v>738</v>
@@ -6569,7 +7498,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>1222</v>
@@ -6643,7 +7572,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>1107</v>
@@ -6717,7 +7646,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>1206</v>
@@ -6791,7 +7720,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>720</v>
@@ -6865,7 +7794,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>654</v>
@@ -6939,7 +7868,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>894</v>
@@ -7013,7 +7942,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>1140</v>
@@ -7087,7 +8016,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="C83">
         <v>1042</v>
@@ -7161,7 +8090,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>822</v>
@@ -7235,7 +8164,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>771</v>
@@ -7309,7 +8238,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="C86">
         <v>731</v>
@@ -7383,7 +8312,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="C87">
         <v>685</v>
@@ -7457,7 +8386,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>868</v>
@@ -7531,7 +8460,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>570</v>
@@ -7605,7 +8534,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>1214</v>
@@ -7679,7 +8608,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>1229</v>
@@ -7753,7 +8682,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>757</v>
@@ -7827,7 +8756,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>33</v>
+        <v>115</v>
       </c>
       <c r="C93">
         <v>679</v>
@@ -7901,7 +8830,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C94">
         <v>936</v>
@@ -7975,7 +8904,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="C95">
         <v>723</v>
@@ -8049,7 +8978,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="C96">
         <v>1208</v>
@@ -8123,7 +9052,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>995</v>
@@ -8197,7 +9126,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="C98">
         <v>632</v>
@@ -8271,7 +9200,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="C99">
         <v>1204</v>
@@ -8345,7 +9274,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="C100">
         <v>1108</v>
@@ -8419,7 +9348,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="C101">
         <v>756</v>
@@ -8493,7 +9422,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="C102">
         <v>775</v>
@@ -8567,7 +9496,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="C103">
         <v>1088</v>
@@ -8641,7 +9570,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="C104">
         <v>1241</v>
@@ -8715,7 +9644,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C105">
         <v>1065</v>
@@ -8789,7 +9718,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="C106">
         <v>1022</v>
@@ -8863,7 +9792,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="C107">
         <v>541</v>
@@ -8937,7 +9866,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="C108">
         <v>942</v>
@@ -9011,7 +9940,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="C109">
         <v>888</v>
@@ -9085,7 +10014,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="C110">
         <v>1105</v>
@@ -9159,7 +10088,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="C111">
         <v>1091</v>
@@ -9233,7 +10162,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="C112">
         <v>782</v>
@@ -9307,7 +10236,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="C113">
         <v>714</v>
@@ -9381,7 +10310,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="C114">
         <v>914</v>
@@ -9455,7 +10384,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="C115">
         <v>788</v>
@@ -9529,7 +10458,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="C116">
         <v>741</v>
@@ -9603,7 +10532,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>138</v>
       </c>
       <c r="C117">
         <v>1128</v>
@@ -9677,7 +10606,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="C118">
         <v>710</v>
@@ -9751,7 +10680,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="C119">
         <v>629</v>
@@ -9825,7 +10754,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="C120">
         <v>1086</v>
@@ -9899,7 +10828,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="C121">
         <v>1191</v>
@@ -9973,7 +10902,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="C122">
         <v>1059</v>
@@ -10047,7 +10976,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="C123">
         <v>977</v>
@@ -10121,7 +11050,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="C124">
         <v>534</v>
@@ -10195,7 +11124,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="C125">
         <v>1064</v>
@@ -10269,7 +11198,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="C126">
         <v>967</v>
@@ -10343,7 +11272,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="C127">
         <v>1013</v>
@@ -10417,7 +11346,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="C128">
         <v>859</v>
@@ -10491,7 +11420,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="C129">
         <v>459</v>
@@ -10565,7 +11494,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="C130">
         <v>1226</v>
@@ -10639,7 +11568,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>68</v>
+        <v>152</v>
       </c>
       <c r="C131">
         <v>841</v>
@@ -10713,7 +11642,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="C132">
         <v>1148</v>
@@ -10787,7 +11716,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="C133">
         <v>979</v>
@@ -10861,7 +11790,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="C134">
         <v>401</v>
@@ -10935,7 +11864,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="C135">
         <v>626</v>
@@ -11009,7 +11938,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>17</v>
+        <v>157</v>
       </c>
       <c r="C136">
         <v>519</v>
@@ -11083,7 +12012,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="C137">
         <v>1219</v>
@@ -11157,7 +12086,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>84</v>
+        <v>159</v>
       </c>
       <c r="C138">
         <v>1134</v>
@@ -11231,7 +12160,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="C139">
         <v>1127</v>
@@ -11305,7 +12234,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="C140">
         <v>729</v>
@@ -11379,7 +12308,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="C141">
         <v>681</v>
@@ -11453,7 +12382,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>99</v>
+        <v>163</v>
       </c>
       <c r="C142">
         <v>662</v>
@@ -11527,7 +12456,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="C143">
         <v>1075</v>
@@ -11601,7 +12530,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="C144">
         <v>682</v>
@@ -11675,7 +12604,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>101</v>
+        <v>166</v>
       </c>
       <c r="C145">
         <v>1070</v>
@@ -11749,7 +12678,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="C146">
         <v>1072</v>
@@ -11823,7 +12752,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="C147">
         <v>1154</v>
@@ -11897,7 +12826,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="C148">
         <v>1192</v>
@@ -11971,7 +12900,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c r="C149">
         <v>687</v>
@@ -12045,7 +12974,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="C150">
         <v>808</v>
@@ -12119,7 +13048,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="C151">
         <v>1037</v>
@@ -12193,7 +13122,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="C152">
         <v>1048</v>
@@ -12267,7 +13196,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="C153">
         <v>1045</v>
@@ -12341,7 +13270,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="C154">
         <v>840</v>
@@ -12415,7 +13344,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>47</v>
+        <v>176</v>
       </c>
       <c r="C155">
         <v>893</v>
@@ -12489,7 +13418,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>47</v>
+        <v>177</v>
       </c>
       <c r="C156">
         <v>1163</v>
@@ -12563,7 +13492,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="C157">
         <v>868</v>
@@ -12637,7 +13566,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="C158">
         <v>934</v>
@@ -12711,7 +13640,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="C159">
         <v>911</v>
@@ -12785,7 +13714,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="C160">
         <v>1100</v>
@@ -12859,7 +13788,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="C161">
         <v>1017</v>
@@ -12933,7 +13862,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>113</v>
+        <v>183</v>
       </c>
       <c r="C162">
         <v>694</v>
@@ -13007,7 +13936,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="C163">
         <v>1095</v>
@@ -13081,7 +14010,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>50</v>
+        <v>185</v>
       </c>
       <c r="C164">
         <v>773</v>
@@ -13155,7 +14084,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="C165">
         <v>1054</v>
@@ -13229,7 +14158,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>111</v>
+        <v>187</v>
       </c>
       <c r="C166">
         <v>733</v>
@@ -13303,7 +14232,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>37</v>
+        <v>188</v>
       </c>
       <c r="C167">
         <v>686</v>
@@ -13377,7 +14306,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="C168">
         <v>686</v>
@@ -13451,7 +14380,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>15</v>
+        <v>190</v>
       </c>
       <c r="C169">
         <v>805</v>
@@ -13525,7 +14454,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="C170">
         <v>478</v>
@@ -13599,7 +14528,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
       <c r="C171">
         <v>404</v>
@@ -13673,7 +14602,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="C172">
         <v>709</v>
@@ -13747,7 +14676,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="C173">
         <v>752</v>
@@ -13821,7 +14750,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>119</v>
+        <v>195</v>
       </c>
       <c r="C174">
         <v>706</v>
@@ -13895,7 +14824,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>120</v>
+        <v>196</v>
       </c>
       <c r="C175">
         <v>1206</v>
@@ -13969,7 +14898,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="C176">
         <v>896</v>
@@ -14043,7 +14972,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="C177">
         <v>828</v>
@@ -14117,7 +15046,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>83</v>
+        <v>199</v>
       </c>
       <c r="C178">
         <v>724</v>
@@ -14191,7 +15120,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="C179">
         <v>682</v>
@@ -14265,7 +15194,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>122</v>
+        <v>201</v>
       </c>
       <c r="C180">
         <v>949</v>
@@ -14339,7 +15268,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="C181">
         <v>1006</v>
@@ -14413,7 +15342,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>11</v>
+        <v>203</v>
       </c>
       <c r="C182">
         <v>639</v>
@@ -14487,7 +15416,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>12</v>
+        <v>204</v>
       </c>
       <c r="C183">
         <v>796</v>
@@ -14561,7 +15490,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C184">
         <v>543</v>
@@ -14635,7 +15564,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>23</v>
+        <v>206</v>
       </c>
       <c r="C185">
         <v>1203</v>
@@ -14709,7 +15638,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>24</v>
+        <v>207</v>
       </c>
       <c r="C186">
         <v>719</v>
@@ -14783,7 +15712,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="C187">
         <v>524</v>
@@ -14857,7 +15786,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="C188">
         <v>842</v>
@@ -14931,7 +15860,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="C189">
         <v>804</v>
@@ -15005,7 +15934,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="C190">
         <v>1026</v>
@@ -15079,7 +16008,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>113</v>
+        <v>212</v>
       </c>
       <c r="C191">
         <v>743</v>
@@ -15153,7 +16082,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="C192">
         <v>739</v>
@@ -15227,7 +16156,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>68</v>
+        <v>214</v>
       </c>
       <c r="C193">
         <v>1151</v>
@@ -15301,7 +16230,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>96</v>
+        <v>215</v>
       </c>
       <c r="C194">
         <v>904</v>
@@ -15375,7 +16304,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>15</v>
+        <v>216</v>
       </c>
       <c r="C195">
         <v>306</v>
@@ -15449,7 +16378,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="C196">
         <v>700</v>
@@ -15523,7 +16452,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>84</v>
+        <v>218</v>
       </c>
       <c r="C197">
         <v>602</v>
@@ -15597,7 +16526,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>60</v>
+        <v>219</v>
       </c>
       <c r="C198">
         <v>769</v>
@@ -15671,7 +16600,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>124</v>
+        <v>220</v>
       </c>
       <c r="C199">
         <v>577</v>
@@ -15745,7 +16674,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>65</v>
+        <v>221</v>
       </c>
       <c r="C200">
         <v>645</v>
@@ -15819,7 +16748,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="C201">
         <v>703</v>
@@ -15893,7 +16822,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>68</v>
+        <v>223</v>
       </c>
       <c r="C202">
         <v>688</v>
@@ -15967,7 +16896,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>69</v>
+        <v>224</v>
       </c>
       <c r="C203">
         <v>702</v>
@@ -16041,7 +16970,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>15</v>
+        <v>225</v>
       </c>
       <c r="C204">
         <v>699</v>
@@ -16115,7 +17044,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="C205">
         <v>949</v>
@@ -16189,7 +17118,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>68</v>
+        <v>227</v>
       </c>
       <c r="C206">
         <v>907</v>
@@ -16263,7 +17192,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>96</v>
+        <v>228</v>
       </c>
       <c r="C207">
         <v>899</v>
@@ -16337,7 +17266,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>126</v>
+        <v>229</v>
       </c>
       <c r="C208">
         <v>947</v>
@@ -16411,7 +17340,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>63</v>
+        <v>230</v>
       </c>
       <c r="C209">
         <v>1024</v>
@@ -16485,7 +17414,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>127</v>
+        <v>231</v>
       </c>
       <c r="C210">
         <v>762</v>
@@ -16559,7 +17488,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>68</v>
+        <v>232</v>
       </c>
       <c r="C211">
         <v>746</v>
@@ -16633,7 +17562,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="C212">
         <v>843</v>
@@ -16707,7 +17636,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>51</v>
+        <v>234</v>
       </c>
       <c r="C213">
         <v>715</v>
@@ -16781,7 +17710,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>52</v>
+        <v>235</v>
       </c>
       <c r="C214">
         <v>754</v>
@@ -16855,7 +17784,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>22</v>
+        <v>236</v>
       </c>
       <c r="C215">
         <v>946</v>
@@ -16929,7 +17858,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>113</v>
+        <v>237</v>
       </c>
       <c r="C216">
         <v>751</v>
@@ -17003,7 +17932,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>112</v>
+        <v>238</v>
       </c>
       <c r="C217">
         <v>672</v>
@@ -17077,7 +18006,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>27</v>
+        <v>239</v>
       </c>
       <c r="C218">
         <v>1079</v>
@@ -17151,7 +18080,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>28</v>
+        <v>240</v>
       </c>
       <c r="C219">
         <v>700</v>
@@ -17225,7 +18154,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>128</v>
+        <v>241</v>
       </c>
       <c r="C220">
         <v>833</v>
@@ -17299,7 +18228,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>129</v>
+        <v>242</v>
       </c>
       <c r="C221">
         <v>1017</v>
@@ -17373,7 +18302,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>17</v>
+        <v>243</v>
       </c>
       <c r="C222">
         <v>556</v>
@@ -17447,7 +18376,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>22</v>
+        <v>244</v>
       </c>
       <c r="C223">
         <v>682</v>
@@ -17521,7 +18450,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>117</v>
+        <v>245</v>
       </c>
       <c r="C224">
         <v>647</v>
@@ -17595,7 +18524,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>63</v>
+        <v>246</v>
       </c>
       <c r="C225">
         <v>785</v>
@@ -17669,7 +18598,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>127</v>
+        <v>247</v>
       </c>
       <c r="C226">
         <v>800</v>
@@ -17743,7 +18672,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>27</v>
+        <v>248</v>
       </c>
       <c r="C227">
         <v>707</v>
@@ -17817,7 +18746,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>28</v>
+        <v>249</v>
       </c>
       <c r="C228">
         <v>863</v>
@@ -17891,7 +18820,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="C229">
         <v>611</v>
@@ -17965,7 +18894,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="C230">
         <v>704</v>
@@ -18039,7 +18968,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="C231">
         <v>1193</v>
@@ -18113,7 +19042,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>133</v>
+        <v>253</v>
       </c>
       <c r="C232">
         <v>1184</v>
@@ -18187,7 +19116,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>134</v>
+        <v>254</v>
       </c>
       <c r="C233">
         <v>749</v>
@@ -18261,7 +19190,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>135</v>
+        <v>255</v>
       </c>
       <c r="C234">
         <v>638</v>
@@ -18335,7 +19264,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>117</v>
+        <v>256</v>
       </c>
       <c r="C235">
         <v>1221</v>
@@ -18409,7 +19338,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>11</v>
+        <v>257</v>
       </c>
       <c r="C236">
         <v>734</v>
@@ -18483,7 +19412,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>12</v>
+        <v>258</v>
       </c>
       <c r="C237">
         <v>822</v>
@@ -18557,7 +19486,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>70</v>
+        <v>259</v>
       </c>
       <c r="C238">
         <v>1106</v>
@@ -18631,7 +19560,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>114</v>
+        <v>260</v>
       </c>
       <c r="C239">
         <v>921</v>
@@ -18705,7 +19634,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>136</v>
+        <v>261</v>
       </c>
       <c r="C240">
         <v>1108</v>
@@ -18779,7 +19708,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>137</v>
+        <v>262</v>
       </c>
       <c r="C241">
         <v>1020</v>
@@ -18853,7 +19782,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>15</v>
+        <v>263</v>
       </c>
       <c r="C242">
         <v>695</v>
@@ -18927,7 +19856,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>13</v>
+        <v>264</v>
       </c>
       <c r="C243">
         <v>882</v>
@@ -19001,7 +19930,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>138</v>
+        <v>265</v>
       </c>
       <c r="C244">
         <v>706</v>
@@ -19075,7 +20004,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="C245">
         <v>904</v>
@@ -19149,7 +20078,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="C246">
         <v>686</v>
@@ -19223,7 +20152,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>123</v>
+        <v>268</v>
       </c>
       <c r="C247">
         <v>595</v>
@@ -19297,7 +20226,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>78</v>
+        <v>269</v>
       </c>
       <c r="C248">
         <v>1161</v>
@@ -19371,7 +20300,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>110</v>
+        <v>270</v>
       </c>
       <c r="C249">
         <v>622</v>
@@ -19445,7 +20374,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>139</v>
+        <v>271</v>
       </c>
       <c r="C250">
         <v>1011</v>
@@ -19519,7 +20448,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>140</v>
+        <v>272</v>
       </c>
       <c r="C251">
         <v>951</v>
@@ -19593,7 +20522,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>101</v>
+        <v>273</v>
       </c>
       <c r="C252">
         <v>998</v>
@@ -19667,7 +20596,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>29</v>
+        <v>274</v>
       </c>
       <c r="C253">
         <v>1147</v>
@@ -19741,7 +20670,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>141</v>
+        <v>275</v>
       </c>
       <c r="C254">
         <v>1061</v>
@@ -19815,7 +20744,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>142</v>
+        <v>276</v>
       </c>
       <c r="C255">
         <v>949</v>
@@ -19889,7 +20818,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>143</v>
+        <v>277</v>
       </c>
       <c r="C256">
         <v>808</v>
@@ -19963,7 +20892,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>95</v>
+        <v>278</v>
       </c>
       <c r="C257">
         <v>1180</v>
@@ -20037,7 +20966,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>126</v>
+        <v>279</v>
       </c>
       <c r="C258">
         <v>843</v>
@@ -20111,7 +21040,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>47</v>
+        <v>280</v>
       </c>
       <c r="C259">
         <v>693</v>
@@ -20185,7 +21114,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>144</v>
+        <v>281</v>
       </c>
       <c r="C260">
         <v>1122</v>
@@ -20259,7 +21188,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>125</v>
+        <v>282</v>
       </c>
       <c r="C261">
         <v>736</v>
@@ -20333,7 +21262,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>22</v>
+        <v>283</v>
       </c>
       <c r="C262">
         <v>980</v>
@@ -20407,7 +21336,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>50</v>
+        <v>284</v>
       </c>
       <c r="C263">
         <v>1065</v>
@@ -20481,7 +21410,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>145</v>
+        <v>285</v>
       </c>
       <c r="C264">
         <v>957</v>
@@ -20555,7 +21484,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>50</v>
+        <v>286</v>
       </c>
       <c r="C265">
         <v>1124</v>
@@ -20629,7 +21558,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>17</v>
+        <v>287</v>
       </c>
       <c r="C266">
         <v>764</v>
@@ -20703,7 +21632,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>146</v>
+        <v>288</v>
       </c>
       <c r="C267">
         <v>1000</v>
@@ -20777,7 +21706,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>147</v>
+        <v>289</v>
       </c>
       <c r="C268">
         <v>1139</v>
@@ -20851,7 +21780,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>125</v>
+        <v>290</v>
       </c>
       <c r="C269">
         <v>1178</v>
@@ -20925,7 +21854,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>101</v>
+        <v>291</v>
       </c>
       <c r="C270">
         <v>1105</v>
@@ -20999,7 +21928,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>68</v>
+        <v>292</v>
       </c>
       <c r="C271">
         <v>1193</v>
@@ -21073,7 +22002,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>69</v>
+        <v>293</v>
       </c>
       <c r="C272">
         <v>828</v>
@@ -21147,7 +22076,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>148</v>
+        <v>294</v>
       </c>
       <c r="C273">
         <v>1119</v>
@@ -21221,7 +22150,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>149</v>
+        <v>295</v>
       </c>
       <c r="C274">
         <v>1118</v>
@@ -21295,7 +22224,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>53</v>
+        <v>296</v>
       </c>
       <c r="C275">
         <v>694</v>
@@ -21369,7 +22298,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="C276">
         <v>784</v>
@@ -21443,7 +22372,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>113</v>
+        <v>298</v>
       </c>
       <c r="C277">
         <v>1144</v>
@@ -21517,7 +22446,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>150</v>
+        <v>299</v>
       </c>
       <c r="C278">
         <v>968</v>
@@ -21591,7 +22520,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="C279">
         <v>1044</v>
@@ -21665,7 +22594,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>151</v>
+        <v>301</v>
       </c>
       <c r="C280">
         <v>889</v>
@@ -21739,7 +22668,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>152</v>
+        <v>302</v>
       </c>
       <c r="C281">
         <v>487</v>
@@ -21813,7 +22742,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>31</v>
+        <v>303</v>
       </c>
       <c r="C282">
         <v>660</v>
@@ -21887,7 +22816,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>32</v>
+        <v>304</v>
       </c>
       <c r="C283">
         <v>641</v>
@@ -21961,7 +22890,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>126</v>
+        <v>305</v>
       </c>
       <c r="C284">
         <v>1117</v>
@@ -22035,7 +22964,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>153</v>
+        <v>306</v>
       </c>
       <c r="C285">
         <v>784</v>
@@ -22109,7 +23038,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>154</v>
+        <v>307</v>
       </c>
       <c r="C286">
         <v>638</v>
@@ -22183,7 +23112,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>63</v>
+        <v>308</v>
       </c>
       <c r="C287">
         <v>658</v>
@@ -22257,7 +23186,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>127</v>
+        <v>309</v>
       </c>
       <c r="C288">
         <v>855</v>
@@ -22331,7 +23260,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>27</v>
+        <v>310</v>
       </c>
       <c r="C289">
         <v>1137</v>
@@ -22405,7 +23334,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>28</v>
+        <v>311</v>
       </c>
       <c r="C290">
         <v>667</v>
@@ -22479,7 +23408,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>65</v>
+        <v>312</v>
       </c>
       <c r="C291">
         <v>1092</v>
@@ -22553,7 +23482,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>155</v>
+        <v>313</v>
       </c>
       <c r="C292">
         <v>1138</v>
@@ -22627,7 +23556,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>42</v>
+        <v>314</v>
       </c>
       <c r="C293">
         <v>805</v>
@@ -22701,7 +23630,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>43</v>
+        <v>315</v>
       </c>
       <c r="C294">
         <v>1168</v>
@@ -22775,7 +23704,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>156</v>
+        <v>316</v>
       </c>
       <c r="C295">
         <v>1046</v>
@@ -22849,7 +23778,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="C296">
         <v>1239</v>
@@ -22923,7 +23852,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>102</v>
+        <v>318</v>
       </c>
       <c r="C297">
         <v>1104</v>
@@ -22997,7 +23926,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>117</v>
+        <v>319</v>
       </c>
       <c r="C298">
         <v>728</v>
@@ -23071,7 +24000,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>60</v>
+        <v>320</v>
       </c>
       <c r="C299">
         <v>732</v>
@@ -23145,7 +24074,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>124</v>
+        <v>321</v>
       </c>
       <c r="C300">
         <v>594</v>
@@ -23219,7 +24148,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>63</v>
+        <v>322</v>
       </c>
       <c r="C301">
         <v>913</v>
@@ -23293,7 +24222,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>127</v>
+        <v>323</v>
       </c>
       <c r="C302">
         <v>1034</v>
@@ -23367,7 +24296,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>17</v>
+        <v>324</v>
       </c>
       <c r="C303">
         <v>865</v>
@@ -23441,7 +24370,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>157</v>
+        <v>325</v>
       </c>
       <c r="C304">
         <v>963</v>
@@ -23515,7 +24444,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>114</v>
+        <v>326</v>
       </c>
       <c r="C305">
         <v>951</v>
@@ -23589,7 +24518,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>158</v>
+        <v>327</v>
       </c>
       <c r="C306">
         <v>980</v>
@@ -23663,7 +24592,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>159</v>
+        <v>328</v>
       </c>
       <c r="C307">
         <v>1022</v>
@@ -23737,7 +24666,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>160</v>
+        <v>329</v>
       </c>
       <c r="C308">
         <v>1124</v>
@@ -23811,7 +24740,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>161</v>
+        <v>330</v>
       </c>
       <c r="C309">
         <v>1120</v>
@@ -23885,7 +24814,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>162</v>
+        <v>331</v>
       </c>
       <c r="C310">
         <v>669</v>
@@ -23959,7 +24888,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>163</v>
+        <v>332</v>
       </c>
       <c r="C311">
         <v>557</v>
@@ -24033,7 +24962,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>164</v>
+        <v>333</v>
       </c>
       <c r="C312">
         <v>835</v>
@@ -24107,7 +25036,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>165</v>
+        <v>334</v>
       </c>
       <c r="C313">
         <v>904</v>
@@ -24181,7 +25110,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>70</v>
+        <v>335</v>
       </c>
       <c r="C314">
         <v>750</v>
@@ -24255,7 +25184,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>18</v>
+        <v>336</v>
       </c>
       <c r="C315">
         <v>830</v>
@@ -24329,7 +25258,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>94</v>
+        <v>337</v>
       </c>
       <c r="C316">
         <v>1037</v>
@@ -24403,7 +25332,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>166</v>
+        <v>338</v>
       </c>
       <c r="C317">
         <v>990</v>
@@ -24477,7 +25406,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>51</v>
+        <v>339</v>
       </c>
       <c r="C318">
         <v>948</v>
@@ -24551,7 +25480,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>52</v>
+        <v>340</v>
       </c>
       <c r="C319">
         <v>646</v>
@@ -24625,7 +25554,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>18</v>
+        <v>341</v>
       </c>
       <c r="C320">
         <v>639</v>
@@ -24699,7 +25628,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>94</v>
+        <v>342</v>
       </c>
       <c r="C321">
         <v>660</v>
@@ -24773,7 +25702,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>125</v>
+        <v>343</v>
       </c>
       <c r="C322">
         <v>1002</v>
@@ -24847,7 +25776,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>61</v>
+        <v>344</v>
       </c>
       <c r="C323">
         <v>798</v>
@@ -24921,7 +25850,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>167</v>
+        <v>345</v>
       </c>
       <c r="C324">
         <v>520</v>
@@ -24995,7 +25924,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>168</v>
+        <v>346</v>
       </c>
       <c r="C325">
         <v>1116</v>
@@ -25069,7 +25998,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>169</v>
+        <v>347</v>
       </c>
       <c r="C326">
         <v>1145</v>
@@ -25143,7 +26072,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>61</v>
+        <v>348</v>
       </c>
       <c r="C327">
         <v>1039</v>
@@ -25217,7 +26146,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>62</v>
+        <v>349</v>
       </c>
       <c r="C328">
         <v>883</v>
@@ -25291,7 +26220,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>167</v>
+        <v>350</v>
       </c>
       <c r="C329">
         <v>844</v>
@@ -25365,7 +26294,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>13</v>
+        <v>351</v>
       </c>
       <c r="C330">
         <v>754</v>
@@ -25439,7 +26368,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>14</v>
+        <v>352</v>
       </c>
       <c r="C331">
         <v>879</v>
@@ -25513,7 +26442,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>170</v>
+        <v>353</v>
       </c>
       <c r="C332">
         <v>976</v>
@@ -25587,7 +26516,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>171</v>
+        <v>354</v>
       </c>
       <c r="C333">
         <v>993</v>
@@ -25661,7 +26590,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>148</v>
+        <v>355</v>
       </c>
       <c r="C334">
         <v>1174</v>
@@ -25735,7 +26664,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>172</v>
+        <v>356</v>
       </c>
       <c r="C335">
         <v>1104</v>
@@ -25809,7 +26738,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>173</v>
+        <v>357</v>
       </c>
       <c r="C336">
         <v>1080</v>
@@ -25883,7 +26812,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>174</v>
+        <v>358</v>
       </c>
       <c r="C337">
         <v>669</v>
@@ -25957,7 +26886,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>175</v>
+        <v>359</v>
       </c>
       <c r="C338">
         <v>609</v>
@@ -26031,7 +26960,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>15</v>
+        <v>360</v>
       </c>
       <c r="C339">
         <v>521</v>
@@ -26105,7 +27034,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>70</v>
+        <v>361</v>
       </c>
       <c r="C340">
         <v>563</v>
@@ -26179,7 +27108,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>25</v>
+        <v>362</v>
       </c>
       <c r="C341">
         <v>720</v>
@@ -26253,7 +27182,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>26</v>
+        <v>363</v>
       </c>
       <c r="C342">
         <v>849</v>
@@ -26327,7 +27256,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>176</v>
+        <v>364</v>
       </c>
       <c r="C343">
         <v>624</v>
@@ -26401,7 +27330,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>177</v>
+        <v>365</v>
       </c>
       <c r="C344">
         <v>701</v>
@@ -26475,7 +27404,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>178</v>
+        <v>366</v>
       </c>
       <c r="C345">
         <v>960</v>
@@ -26549,7 +27478,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>13</v>
+        <v>367</v>
       </c>
       <c r="C346">
         <v>980</v>
@@ -26623,7 +27552,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>14</v>
+        <v>368</v>
       </c>
       <c r="C347">
         <v>674</v>
@@ -26697,7 +27626,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>179</v>
+        <v>369</v>
       </c>
       <c r="C348">
         <v>956</v>
@@ -26771,7 +27700,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>180</v>
+        <v>370</v>
       </c>
       <c r="C349">
         <v>937</v>
@@ -26845,7 +27774,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>181</v>
+        <v>230</v>
       </c>
       <c r="C350">
         <v>1205</v>
@@ -26919,7 +27848,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>182</v>
+        <v>371</v>
       </c>
       <c r="C351">
         <v>1174</v>
@@ -26993,7 +27922,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>18</v>
+        <v>372</v>
       </c>
       <c r="C352">
         <v>1021</v>
@@ -27067,7 +27996,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>94</v>
+        <v>373</v>
       </c>
       <c r="C353">
         <v>1087</v>
@@ -27141,7 +28070,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>183</v>
+        <v>374</v>
       </c>
       <c r="C354">
         <v>909</v>
@@ -27215,7 +28144,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>184</v>
+        <v>375</v>
       </c>
       <c r="C355">
         <v>890</v>
@@ -27289,7 +28218,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>185</v>
+        <v>376</v>
       </c>
       <c r="C356">
         <v>1139</v>
@@ -27363,7 +28292,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>186</v>
+        <v>377</v>
       </c>
       <c r="C357">
         <v>626</v>
@@ -27437,7 +28366,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>187</v>
+        <v>378</v>
       </c>
       <c r="C358">
         <v>641</v>
@@ -27511,7 +28440,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>188</v>
+        <v>379</v>
       </c>
       <c r="C359">
         <v>1102</v>
@@ -27585,7 +28514,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>189</v>
+        <v>380</v>
       </c>
       <c r="C360">
         <v>696</v>
@@ -27659,7 +28588,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>190</v>
+        <v>381</v>
       </c>
       <c r="C361">
         <v>911</v>
@@ -27733,7 +28662,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>191</v>
+        <v>382</v>
       </c>
       <c r="C362">
         <v>1083</v>
@@ -27807,7 +28736,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>192</v>
+        <v>383</v>
       </c>
       <c r="C363">
         <v>781</v>
@@ -27881,7 +28810,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>193</v>
+        <v>384</v>
       </c>
       <c r="C364">
         <v>688</v>
@@ -27955,7 +28884,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>194</v>
+        <v>385</v>
       </c>
       <c r="C365">
         <v>640</v>
@@ -28029,7 +28958,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>195</v>
+        <v>386</v>
       </c>
       <c r="C366">
         <v>1070</v>
@@ -28103,7 +29032,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>196</v>
+        <v>387</v>
       </c>
       <c r="C367">
         <v>1036</v>
@@ -28177,7 +29106,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>197</v>
+        <v>388</v>
       </c>
       <c r="C368">
         <v>793</v>
@@ -28251,7 +29180,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>148</v>
+        <v>389</v>
       </c>
       <c r="C369">
         <v>1108</v>
@@ -28325,7 +29254,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>149</v>
+        <v>390</v>
       </c>
       <c r="C370">
         <v>996</v>
@@ -28399,7 +29328,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>42</v>
+        <v>391</v>
       </c>
       <c r="C371">
         <v>1022</v>
@@ -28473,7 +29402,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>46</v>
+        <v>392</v>
       </c>
       <c r="C372">
         <v>876</v>
@@ -28547,7 +29476,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>198</v>
+        <v>393</v>
       </c>
       <c r="C373">
         <v>772</v>
@@ -28621,7 +29550,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>18</v>
+        <v>394</v>
       </c>
       <c r="C374">
         <v>696</v>
@@ -28695,7 +29624,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>19</v>
+        <v>395</v>
       </c>
       <c r="C375">
         <v>850</v>
@@ -28769,7 +29698,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>22</v>
+        <v>396</v>
       </c>
       <c r="C376">
         <v>370</v>
@@ -28843,7 +29772,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>116</v>
+        <v>397</v>
       </c>
       <c r="C377">
         <v>393</v>
@@ -28917,7 +29846,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>15</v>
+        <v>398</v>
       </c>
       <c r="C378">
         <v>538</v>
@@ -28991,7 +29920,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>13</v>
+        <v>399</v>
       </c>
       <c r="C379">
         <v>751</v>
@@ -29065,7 +29994,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>138</v>
+        <v>400</v>
       </c>
       <c r="C380">
         <v>633</v>
@@ -29139,7 +30068,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>22</v>
+        <v>401</v>
       </c>
       <c r="C381">
         <v>1005</v>
@@ -29213,7 +30142,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>116</v>
+        <v>402</v>
       </c>
       <c r="C382">
         <v>1063</v>
@@ -29287,7 +30216,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>153</v>
+        <v>403</v>
       </c>
       <c r="C383">
         <v>734</v>
@@ -29361,7 +30290,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>154</v>
+        <v>404</v>
       </c>
       <c r="C384">
         <v>778</v>
@@ -29435,7 +30364,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>13</v>
+        <v>405</v>
       </c>
       <c r="C385">
         <v>666</v>
@@ -29509,7 +30438,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>138</v>
+        <v>406</v>
       </c>
       <c r="C386">
         <v>652</v>
@@ -29583,7 +30512,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>50</v>
+        <v>407</v>
       </c>
       <c r="C387">
         <v>1052</v>
@@ -29657,7 +30586,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>199</v>
+        <v>408</v>
       </c>
       <c r="C388">
         <v>597</v>
@@ -29731,7 +30660,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>200</v>
+        <v>409</v>
       </c>
       <c r="C389">
         <v>735</v>
@@ -29805,7 +30734,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="C390">
         <v>879</v>
@@ -29879,7 +30808,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>65</v>
+        <v>411</v>
       </c>
       <c r="C391">
         <v>944</v>
@@ -29953,7 +30882,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>155</v>
+        <v>412</v>
       </c>
       <c r="C392">
         <v>906</v>
@@ -30027,7 +30956,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>117</v>
+        <v>413</v>
       </c>
       <c r="C393">
         <v>704</v>
@@ -30101,7 +31030,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>201</v>
+        <v>414</v>
       </c>
       <c r="C394">
         <v>1007</v>
@@ -30175,7 +31104,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>202</v>
+        <v>415</v>
       </c>
       <c r="C395">
         <v>1006</v>
@@ -30249,7 +31178,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>203</v>
+        <v>416</v>
       </c>
       <c r="C396">
         <v>920</v>
@@ -30323,7 +31252,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>155</v>
+        <v>417</v>
       </c>
       <c r="C397">
         <v>884</v>
@@ -30397,7 +31326,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>65</v>
+        <v>418</v>
       </c>
       <c r="C398">
         <v>1058</v>
@@ -30471,7 +31400,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>67</v>
+        <v>419</v>
       </c>
       <c r="C399">
         <v>1212</v>
@@ -30545,7 +31474,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>13</v>
+        <v>420</v>
       </c>
       <c r="C400">
         <v>917</v>
@@ -30619,7 +31548,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>14</v>
+        <v>421</v>
       </c>
       <c r="C401">
         <v>807</v>
@@ -30693,7 +31622,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>15</v>
+        <v>422</v>
       </c>
       <c r="C402">
         <v>463</v>
@@ -30767,7 +31696,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>170</v>
+        <v>423</v>
       </c>
       <c r="C403">
         <v>874</v>
@@ -30841,7 +31770,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>204</v>
+        <v>424</v>
       </c>
       <c r="C404">
         <v>779</v>
@@ -30915,7 +31844,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>205</v>
+        <v>425</v>
       </c>
       <c r="C405">
         <v>902</v>
@@ -30989,7 +31918,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>65</v>
+        <v>426</v>
       </c>
       <c r="C406">
         <v>711</v>
@@ -31063,7 +31992,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>67</v>
+        <v>427</v>
       </c>
       <c r="C407">
         <v>626</v>
@@ -31137,7 +32066,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>170</v>
+        <v>428</v>
       </c>
       <c r="C408">
         <v>1169</v>
@@ -31211,7 +32140,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>171</v>
+        <v>429</v>
       </c>
       <c r="C409">
         <v>950</v>
@@ -31285,7 +32214,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>95</v>
+        <v>430</v>
       </c>
       <c r="C410">
         <v>1211</v>
@@ -31359,7 +32288,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>77</v>
+        <v>431</v>
       </c>
       <c r="C411">
         <v>652</v>
@@ -31433,7 +32362,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>78</v>
+        <v>432</v>
       </c>
       <c r="C412">
         <v>640</v>
@@ -31507,7 +32436,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>77</v>
+        <v>433</v>
       </c>
       <c r="C413">
         <v>774</v>
@@ -31581,7 +32510,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>123</v>
+        <v>434</v>
       </c>
       <c r="C414">
         <v>722</v>
@@ -31655,7 +32584,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>22</v>
+        <v>435</v>
       </c>
       <c r="C415">
         <v>899</v>
@@ -31729,7 +32658,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>17</v>
+        <v>436</v>
       </c>
       <c r="C416">
         <v>487</v>
@@ -31803,7 +32732,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>206</v>
+        <v>437</v>
       </c>
       <c r="C417">
         <v>1080</v>
@@ -31877,7 +32806,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>207</v>
+        <v>438</v>
       </c>
       <c r="C418">
         <v>699</v>
@@ -31951,7 +32880,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>53</v>
+        <v>439</v>
       </c>
       <c r="C419">
         <v>704</v>
@@ -32025,7 +32954,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>54</v>
+        <v>440</v>
       </c>
       <c r="C420">
         <v>730</v>
@@ -32099,7 +33028,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>208</v>
+        <v>441</v>
       </c>
       <c r="C421">
         <v>1131</v>
@@ -32173,7 +33102,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>209</v>
+        <v>442</v>
       </c>
       <c r="C422">
         <v>999</v>
@@ -32247,7 +33176,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>60</v>
+        <v>443</v>
       </c>
       <c r="C423">
         <v>614</v>
@@ -32321,7 +33250,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>124</v>
+        <v>444</v>
       </c>
       <c r="C424">
         <v>744</v>
@@ -32395,7 +33324,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>210</v>
+        <v>445</v>
       </c>
       <c r="C425">
         <v>1126</v>
@@ -32469,7 +33398,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>211</v>
+        <v>446</v>
       </c>
       <c r="C426">
         <v>665</v>
@@ -32543,7 +33472,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>14</v>
+        <v>447</v>
       </c>
       <c r="C427">
         <v>674</v>
@@ -32617,7 +33546,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>114</v>
+        <v>448</v>
       </c>
       <c r="C428">
         <v>692</v>
@@ -32691,7 +33620,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>15</v>
+        <v>449</v>
       </c>
       <c r="C429">
         <v>480</v>
@@ -32765,7 +33694,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>17</v>
+        <v>450</v>
       </c>
       <c r="C430">
         <v>877</v>
@@ -32839,7 +33768,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>18</v>
+        <v>451</v>
       </c>
       <c r="C431">
         <v>943</v>
@@ -32913,7 +33842,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>94</v>
+        <v>452</v>
       </c>
       <c r="C432">
         <v>832</v>
@@ -32987,7 +33916,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>126</v>
+        <v>453</v>
       </c>
       <c r="C433">
         <v>340</v>
@@ -33061,7 +33990,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>212</v>
+        <v>454</v>
       </c>
       <c r="C434">
         <v>1073</v>
@@ -33135,7 +34064,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>213</v>
+        <v>455</v>
       </c>
       <c r="C435">
         <v>1204</v>
@@ -33209,7 +34138,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>214</v>
+        <v>456</v>
       </c>
       <c r="C436">
         <v>1034</v>
@@ -33283,7 +34212,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>215</v>
+        <v>457</v>
       </c>
       <c r="C437">
         <v>774</v>
@@ -33357,7 +34286,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>70</v>
+        <v>458</v>
       </c>
       <c r="C438">
         <v>740</v>
@@ -33431,7 +34360,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>27</v>
+        <v>459</v>
       </c>
       <c r="C439">
         <v>549</v>
@@ -33505,7 +34434,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>102</v>
+        <v>460</v>
       </c>
       <c r="C440">
         <v>759</v>
@@ -33579,7 +34508,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>28</v>
+        <v>461</v>
       </c>
       <c r="C441">
         <v>1187</v>
@@ -33653,7 +34582,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>11</v>
+        <v>462</v>
       </c>
       <c r="C442">
         <v>709</v>
@@ -33727,7 +34656,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>216</v>
+        <v>463</v>
       </c>
       <c r="C443">
         <v>809</v>
@@ -33801,7 +34730,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>217</v>
+        <v>464</v>
       </c>
       <c r="C444">
         <v>677</v>
@@ -33875,7 +34804,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>218</v>
+        <v>465</v>
       </c>
       <c r="C445">
         <v>647</v>
@@ -33949,7 +34878,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>11</v>
+        <v>466</v>
       </c>
       <c r="C446">
         <v>796</v>
@@ -34023,7 +34952,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>12</v>
+        <v>467</v>
       </c>
       <c r="C447">
         <v>755</v>
@@ -34097,7 +35026,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>111</v>
+        <v>468</v>
       </c>
       <c r="C448">
         <v>688</v>
@@ -34171,7 +35100,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>65</v>
+        <v>469</v>
       </c>
       <c r="C449">
         <v>959</v>
@@ -34245,7 +35174,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>155</v>
+        <v>470</v>
       </c>
       <c r="C450">
         <v>833</v>
@@ -34319,7 +35248,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>47</v>
+        <v>471</v>
       </c>
       <c r="C451">
         <v>490</v>
@@ -34393,7 +35322,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>165</v>
+        <v>472</v>
       </c>
       <c r="C452">
         <v>557</v>
@@ -34467,7 +35396,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>65</v>
+        <v>473</v>
       </c>
       <c r="C453">
         <v>669</v>
@@ -34541,7 +35470,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>155</v>
+        <v>474</v>
       </c>
       <c r="C454">
         <v>1200</v>
@@ -34615,7 +35544,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>67</v>
+        <v>475</v>
       </c>
       <c r="C455">
         <v>900</v>
@@ -34689,7 +35618,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>77</v>
+        <v>476</v>
       </c>
       <c r="C456">
         <v>878</v>
@@ -34763,7 +35692,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>123</v>
+        <v>477</v>
       </c>
       <c r="C457">
         <v>834</v>
@@ -34837,7 +35766,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>219</v>
+        <v>478</v>
       </c>
       <c r="C458">
         <v>814</v>
@@ -34911,7 +35840,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>11</v>
+        <v>479</v>
       </c>
       <c r="C459">
         <v>703</v>
@@ -34985,7 +35914,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>220</v>
+        <v>480</v>
       </c>
       <c r="C460">
         <v>663</v>
@@ -35059,7 +35988,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>221</v>
+        <v>481</v>
       </c>
       <c r="C461">
         <v>805</v>
@@ -35133,7 +36062,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>222</v>
+        <v>482</v>
       </c>
       <c r="C462">
         <v>702</v>
@@ -35207,7 +36136,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>148</v>
+        <v>483</v>
       </c>
       <c r="C463">
         <v>1025</v>
@@ -35281,7 +36210,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>172</v>
+        <v>484</v>
       </c>
       <c r="C464">
         <v>875</v>
@@ -35355,7 +36284,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>18</v>
+        <v>485</v>
       </c>
       <c r="C465">
         <v>725</v>
@@ -35429,7 +36358,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>19</v>
+        <v>486</v>
       </c>
       <c r="C466">
         <v>828</v>
@@ -35503,7 +36432,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>27</v>
+        <v>487</v>
       </c>
       <c r="C467">
         <v>672</v>
@@ -35577,7 +36506,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>28</v>
+        <v>488</v>
       </c>
       <c r="C468">
         <v>605</v>
@@ -35651,7 +36580,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="s">
-        <v>102</v>
+        <v>489</v>
       </c>
       <c r="C469">
         <v>1232</v>
@@ -35725,7 +36654,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>18</v>
+        <v>490</v>
       </c>
       <c r="C470">
         <v>1080</v>
@@ -35799,7 +36728,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="s">
-        <v>94</v>
+        <v>491</v>
       </c>
       <c r="C471">
         <v>691</v>
@@ -35873,7 +36802,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="s">
-        <v>19</v>
+        <v>492</v>
       </c>
       <c r="C472">
         <v>609</v>
@@ -35947,7 +36876,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="s">
-        <v>77</v>
+        <v>493</v>
       </c>
       <c r="C473">
         <v>1168</v>
@@ -36021,7 +36950,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="s">
-        <v>123</v>
+        <v>494</v>
       </c>
       <c r="C474">
         <v>907</v>
@@ -36095,7 +37024,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="s">
-        <v>68</v>
+        <v>495</v>
       </c>
       <c r="C475">
         <v>1061</v>
@@ -36169,7 +37098,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="s">
-        <v>69</v>
+        <v>496</v>
       </c>
       <c r="C476">
         <v>1083</v>
@@ -36243,7 +37172,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="s">
-        <v>27</v>
+        <v>497</v>
       </c>
       <c r="C477">
         <v>876</v>
@@ -36317,7 +37246,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="s">
-        <v>28</v>
+        <v>498</v>
       </c>
       <c r="C478">
         <v>937</v>
@@ -36391,7 +37320,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="s">
-        <v>11</v>
+        <v>499</v>
       </c>
       <c r="C479">
         <v>818</v>
@@ -36465,7 +37394,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="s">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="C480">
         <v>773</v>
